--- a/exit/Meta49_preenchido.xlsx
+++ b/exit/Meta49_preenchido.xlsx
@@ -12895,9 +12895,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D4" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D4" s="116" t="n"/>
       <c r="E4" s="116" t="n"/>
       <c r="F4" s="116" t="n"/>
       <c r="G4" s="116" t="n"/>
@@ -12929,9 +12927,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D5" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D5" s="119" t="n"/>
       <c r="E5" s="119" t="n"/>
       <c r="F5" s="119" t="n"/>
       <c r="G5" s="119" t="n"/>
@@ -12963,9 +12959,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D6" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D6" s="119" t="n"/>
       <c r="E6" s="119" t="n"/>
       <c r="F6" s="119" t="n"/>
       <c r="G6" s="119" t="n"/>
@@ -12997,9 +12991,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D7" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D7" s="116" t="n"/>
       <c r="E7" s="116" t="n"/>
       <c r="F7" s="116" t="n"/>
       <c r="G7" s="116" t="n"/>
@@ -13031,9 +13023,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D8" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D8" s="119" t="n"/>
       <c r="E8" s="119" t="n"/>
       <c r="F8" s="119" t="n"/>
       <c r="G8" s="119" t="n"/>
@@ -13065,9 +13055,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D9" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D9" s="119" t="n"/>
       <c r="E9" s="119" t="n"/>
       <c r="F9" s="119" t="n"/>
       <c r="G9" s="119" t="n"/>
@@ -13099,9 +13087,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D10" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D10" s="116" t="n"/>
       <c r="E10" s="116" t="n"/>
       <c r="F10" s="116" t="n"/>
       <c r="G10" s="116" t="n"/>
@@ -13133,9 +13119,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D11" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D11" s="119" t="n"/>
       <c r="E11" s="119" t="n"/>
       <c r="F11" s="119" t="n"/>
       <c r="G11" s="119" t="n"/>
@@ -13167,9 +13151,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D12" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D12" s="119" t="n"/>
       <c r="E12" s="119" t="n"/>
       <c r="F12" s="119" t="n"/>
       <c r="G12" s="119" t="n"/>
@@ -13204,19 +13186,39 @@
       <c r="D13" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="116" t="n"/>
+      <c r="E13" s="116" t="n">
+        <v>25308</v>
+      </c>
       <c r="F13" s="116" t="n"/>
-      <c r="G13" s="116" t="n"/>
-      <c r="H13" s="116" t="n"/>
-      <c r="I13" s="116" t="n"/>
-      <c r="J13" s="116" t="n"/>
-      <c r="K13" s="116" t="n"/>
-      <c r="L13" s="116" t="n"/>
-      <c r="M13" s="116" t="n"/>
-      <c r="N13" s="116" t="n"/>
-      <c r="O13" s="116" t="n"/>
+      <c r="G13" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="P13" s="116" t="n">
-        <v>0</v>
+        <v>25308</v>
       </c>
     </row>
     <row r="14" ht="35.25" customHeight="1" s="134">
@@ -13238,17 +13240,37 @@
       <c r="D14" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="119" t="n"/>
+      <c r="E14" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F14" s="119" t="n"/>
-      <c r="G14" s="119" t="n"/>
-      <c r="H14" s="119" t="n"/>
-      <c r="I14" s="119" t="n"/>
-      <c r="J14" s="119" t="n"/>
-      <c r="K14" s="119" t="n"/>
-      <c r="L14" s="119" t="n"/>
-      <c r="M14" s="119" t="n"/>
-      <c r="N14" s="119" t="n"/>
-      <c r="O14" s="119" t="n"/>
+      <c r="G14" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P14" s="119" t="n">
         <v>0</v>
       </c>
@@ -13272,19 +13294,39 @@
       <c r="D15" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="119" t="n"/>
+      <c r="E15" s="119" t="n">
+        <v>25308</v>
+      </c>
       <c r="F15" s="119" t="n"/>
-      <c r="G15" s="119" t="n"/>
-      <c r="H15" s="119" t="n"/>
-      <c r="I15" s="119" t="n"/>
-      <c r="J15" s="119" t="n"/>
-      <c r="K15" s="119" t="n"/>
-      <c r="L15" s="119" t="n"/>
-      <c r="M15" s="119" t="n"/>
-      <c r="N15" s="119" t="n"/>
-      <c r="O15" s="119" t="n"/>
+      <c r="G15" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P15" s="119" t="n">
-        <v>0</v>
+        <v>25308</v>
       </c>
     </row>
     <row r="16" ht="35.25" customHeight="1" s="134">
@@ -13303,9 +13345,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D16" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D16" s="116" t="n"/>
       <c r="E16" s="116" t="n"/>
       <c r="F16" s="116" t="n"/>
       <c r="G16" s="116" t="n"/>
@@ -13337,9 +13377,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D17" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D17" s="119" t="n"/>
       <c r="E17" s="119" t="n"/>
       <c r="F17" s="119" t="n"/>
       <c r="G17" s="119" t="n"/>
@@ -13371,9 +13409,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D18" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D18" s="119" t="n"/>
       <c r="E18" s="119" t="n"/>
       <c r="F18" s="119" t="n"/>
       <c r="G18" s="119" t="n"/>
@@ -13405,9 +13441,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D19" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D19" s="116" t="n"/>
       <c r="E19" s="116" t="n"/>
       <c r="F19" s="116" t="n"/>
       <c r="G19" s="116" t="n"/>
@@ -13439,9 +13473,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D20" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D20" s="119" t="n"/>
       <c r="E20" s="119" t="n"/>
       <c r="F20" s="119" t="n"/>
       <c r="G20" s="119" t="n"/>
@@ -13473,9 +13505,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D21" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D21" s="119" t="n"/>
       <c r="E21" s="119" t="n"/>
       <c r="F21" s="119" t="n"/>
       <c r="G21" s="119" t="n"/>
@@ -13510,19 +13540,39 @@
       <c r="D22" s="116" t="n">
         <v>17631</v>
       </c>
-      <c r="E22" s="116" t="n"/>
+      <c r="E22" s="116" t="n">
+        <v>3870</v>
+      </c>
       <c r="F22" s="116" t="n"/>
-      <c r="G22" s="116" t="n"/>
-      <c r="H22" s="116" t="n"/>
-      <c r="I22" s="116" t="n"/>
-      <c r="J22" s="116" t="n"/>
-      <c r="K22" s="116" t="n"/>
-      <c r="L22" s="116" t="n"/>
-      <c r="M22" s="116" t="n"/>
-      <c r="N22" s="116" t="n"/>
-      <c r="O22" s="116" t="n"/>
+      <c r="G22" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="P22" s="116" t="n">
-        <v>17631</v>
+        <v>21501</v>
       </c>
     </row>
     <row r="23" ht="35.25" customHeight="1" s="134">
@@ -13544,17 +13594,37 @@
       <c r="D23" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="119" t="n"/>
+      <c r="E23" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F23" s="119" t="n"/>
-      <c r="G23" s="119" t="n"/>
-      <c r="H23" s="119" t="n"/>
-      <c r="I23" s="119" t="n"/>
-      <c r="J23" s="119" t="n"/>
-      <c r="K23" s="119" t="n"/>
-      <c r="L23" s="119" t="n"/>
-      <c r="M23" s="119" t="n"/>
-      <c r="N23" s="119" t="n"/>
-      <c r="O23" s="119" t="n"/>
+      <c r="G23" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P23" s="119" t="n">
         <v>0</v>
       </c>
@@ -13578,19 +13648,39 @@
       <c r="D24" s="119" t="n">
         <v>17631</v>
       </c>
-      <c r="E24" s="119" t="n"/>
+      <c r="E24" s="119" t="n">
+        <v>3870</v>
+      </c>
       <c r="F24" s="119" t="n"/>
-      <c r="G24" s="119" t="n"/>
-      <c r="H24" s="119" t="n"/>
-      <c r="I24" s="119" t="n"/>
-      <c r="J24" s="119" t="n"/>
-      <c r="K24" s="119" t="n"/>
-      <c r="L24" s="119" t="n"/>
-      <c r="M24" s="119" t="n"/>
-      <c r="N24" s="119" t="n"/>
-      <c r="O24" s="119" t="n"/>
+      <c r="G24" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P24" s="119" t="n">
-        <v>17631</v>
+        <v>21501</v>
       </c>
     </row>
     <row r="25" ht="35.25" customHeight="1" s="134">
@@ -13609,9 +13699,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D25" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D25" s="116" t="n"/>
       <c r="E25" s="116" t="n"/>
       <c r="F25" s="116" t="n"/>
       <c r="G25" s="116" t="n"/>
@@ -13643,9 +13731,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D26" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D26" s="119" t="n"/>
       <c r="E26" s="119" t="n"/>
       <c r="F26" s="119" t="n"/>
       <c r="G26" s="119" t="n"/>
@@ -13677,9 +13763,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D27" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D27" s="119" t="n"/>
       <c r="E27" s="119" t="n"/>
       <c r="F27" s="119" t="n"/>
       <c r="G27" s="119" t="n"/>
@@ -13711,9 +13795,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D28" s="116" t="n">
-        <v>2840.1</v>
-      </c>
+      <c r="D28" s="116" t="n"/>
       <c r="E28" s="116" t="n"/>
       <c r="F28" s="116" t="n"/>
       <c r="G28" s="116" t="n"/>
@@ -13726,7 +13808,7 @@
       <c r="N28" s="116" t="n"/>
       <c r="O28" s="116" t="n"/>
       <c r="P28" s="116" t="n">
-        <v>2840.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" ht="35.25" customHeight="1" s="134">
@@ -13745,9 +13827,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D29" s="119" t="n">
-        <v>2840.1</v>
-      </c>
+      <c r="D29" s="119" t="n"/>
       <c r="E29" s="119" t="n"/>
       <c r="F29" s="119" t="n"/>
       <c r="G29" s="119" t="n"/>
@@ -13760,7 +13840,7 @@
       <c r="N29" s="119" t="n"/>
       <c r="O29" s="119" t="n"/>
       <c r="P29" s="119" t="n">
-        <v>2840.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" ht="35.25" customHeight="1" s="134">
@@ -13779,9 +13859,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D30" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D30" s="119" t="n"/>
       <c r="E30" s="119" t="n"/>
       <c r="F30" s="119" t="n"/>
       <c r="G30" s="119" t="n"/>
@@ -13813,9 +13891,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D31" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D31" s="116" t="n"/>
       <c r="E31" s="116" t="n"/>
       <c r="F31" s="116" t="n"/>
       <c r="G31" s="116" t="n"/>
@@ -13847,9 +13923,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D32" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D32" s="119" t="n"/>
       <c r="E32" s="119" t="n"/>
       <c r="F32" s="119" t="n"/>
       <c r="G32" s="119" t="n"/>
@@ -13881,9 +13955,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D33" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D33" s="119" t="n"/>
       <c r="E33" s="119" t="n"/>
       <c r="F33" s="119" t="n"/>
       <c r="G33" s="119" t="n"/>
@@ -13915,9 +13987,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D34" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D34" s="116" t="n"/>
       <c r="E34" s="116" t="n"/>
       <c r="F34" s="116" t="n"/>
       <c r="G34" s="116" t="n"/>
@@ -13949,9 +14019,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D35" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D35" s="119" t="n"/>
       <c r="E35" s="119" t="n"/>
       <c r="F35" s="119" t="n"/>
       <c r="G35" s="119" t="n"/>
@@ -13983,9 +14051,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D36" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D36" s="119" t="n"/>
       <c r="E36" s="119" t="n"/>
       <c r="F36" s="119" t="n"/>
       <c r="G36" s="119" t="n"/>
@@ -14020,19 +14086,39 @@
       <c r="D37" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="116" t="n"/>
+      <c r="E37" s="116" t="n">
+        <v>3760</v>
+      </c>
       <c r="F37" s="116" t="n"/>
-      <c r="G37" s="116" t="n"/>
-      <c r="H37" s="116" t="n"/>
-      <c r="I37" s="116" t="n"/>
-      <c r="J37" s="116" t="n"/>
-      <c r="K37" s="116" t="n"/>
-      <c r="L37" s="116" t="n"/>
-      <c r="M37" s="116" t="n"/>
-      <c r="N37" s="116" t="n"/>
-      <c r="O37" s="116" t="n"/>
+      <c r="G37" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="P37" s="116" t="n">
-        <v>0</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="38" ht="35.25" customHeight="1" s="134">
@@ -14054,17 +14140,37 @@
       <c r="D38" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="119" t="n"/>
+      <c r="E38" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" s="119" t="n"/>
-      <c r="G38" s="119" t="n"/>
-      <c r="H38" s="119" t="n"/>
-      <c r="I38" s="119" t="n"/>
-      <c r="J38" s="119" t="n"/>
-      <c r="K38" s="119" t="n"/>
-      <c r="L38" s="119" t="n"/>
-      <c r="M38" s="119" t="n"/>
-      <c r="N38" s="119" t="n"/>
-      <c r="O38" s="119" t="n"/>
+      <c r="G38" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P38" s="119" t="n">
         <v>0</v>
       </c>
@@ -14088,19 +14194,39 @@
       <c r="D39" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="119" t="n"/>
+      <c r="E39" s="119" t="n">
+        <v>3760</v>
+      </c>
       <c r="F39" s="119" t="n"/>
-      <c r="G39" s="119" t="n"/>
-      <c r="H39" s="119" t="n"/>
-      <c r="I39" s="119" t="n"/>
-      <c r="J39" s="119" t="n"/>
-      <c r="K39" s="119" t="n"/>
-      <c r="L39" s="119" t="n"/>
-      <c r="M39" s="119" t="n"/>
-      <c r="N39" s="119" t="n"/>
-      <c r="O39" s="119" t="n"/>
+      <c r="G39" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P39" s="119" t="n">
-        <v>0</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="40" ht="35.25" customHeight="1" s="134">
@@ -14122,19 +14248,39 @@
       <c r="D40" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="116" t="n"/>
+      <c r="E40" s="116" t="n">
+        <v>3486.51</v>
+      </c>
       <c r="F40" s="116" t="n"/>
-      <c r="G40" s="116" t="n"/>
-      <c r="H40" s="116" t="n"/>
-      <c r="I40" s="116" t="n"/>
-      <c r="J40" s="116" t="n"/>
-      <c r="K40" s="116" t="n"/>
-      <c r="L40" s="116" t="n"/>
-      <c r="M40" s="116" t="n"/>
-      <c r="N40" s="116" t="n"/>
-      <c r="O40" s="116" t="n"/>
+      <c r="G40" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="P40" s="116" t="n">
-        <v>0</v>
+        <v>3486.51</v>
       </c>
     </row>
     <row r="41" ht="35.25" customHeight="1" s="134">
@@ -14156,17 +14302,37 @@
       <c r="D41" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="119" t="n"/>
+      <c r="E41" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F41" s="119" t="n"/>
-      <c r="G41" s="119" t="n"/>
-      <c r="H41" s="119" t="n"/>
-      <c r="I41" s="119" t="n"/>
-      <c r="J41" s="119" t="n"/>
-      <c r="K41" s="119" t="n"/>
-      <c r="L41" s="119" t="n"/>
-      <c r="M41" s="119" t="n"/>
-      <c r="N41" s="119" t="n"/>
-      <c r="O41" s="119" t="n"/>
+      <c r="G41" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P41" s="119" t="n">
         <v>0</v>
       </c>
@@ -14190,19 +14356,39 @@
       <c r="D42" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="119" t="n"/>
+      <c r="E42" s="119" t="n">
+        <v>3486.51</v>
+      </c>
       <c r="F42" s="119" t="n"/>
-      <c r="G42" s="119" t="n"/>
-      <c r="H42" s="119" t="n"/>
-      <c r="I42" s="119" t="n"/>
-      <c r="J42" s="119" t="n"/>
-      <c r="K42" s="119" t="n"/>
-      <c r="L42" s="119" t="n"/>
-      <c r="M42" s="119" t="n"/>
-      <c r="N42" s="119" t="n"/>
-      <c r="O42" s="119" t="n"/>
+      <c r="G42" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P42" s="119" t="n">
-        <v>0</v>
+        <v>3486.51</v>
       </c>
     </row>
     <row r="43" ht="35.25" customHeight="1" s="134">
@@ -14221,9 +14407,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D43" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D43" s="116" t="n"/>
       <c r="E43" s="116" t="n"/>
       <c r="F43" s="116" t="n"/>
       <c r="G43" s="116" t="n"/>
@@ -14255,9 +14439,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D44" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D44" s="119" t="n"/>
       <c r="E44" s="119" t="n"/>
       <c r="F44" s="119" t="n"/>
       <c r="G44" s="119" t="n"/>
@@ -14289,9 +14471,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D45" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D45" s="119" t="n"/>
       <c r="E45" s="119" t="n"/>
       <c r="F45" s="119" t="n"/>
       <c r="G45" s="119" t="n"/>
@@ -14324,21 +14504,41 @@
         </is>
       </c>
       <c r="D46" s="116" t="n">
-        <v>16322.7</v>
-      </c>
-      <c r="E46" s="116" t="n"/>
+        <v>13425</v>
+      </c>
+      <c r="E46" s="116" t="n">
+        <v>18939</v>
+      </c>
       <c r="F46" s="116" t="n"/>
-      <c r="G46" s="116" t="n"/>
-      <c r="H46" s="116" t="n"/>
-      <c r="I46" s="116" t="n"/>
-      <c r="J46" s="116" t="n"/>
-      <c r="K46" s="116" t="n"/>
-      <c r="L46" s="116" t="n"/>
-      <c r="M46" s="116" t="n"/>
-      <c r="N46" s="116" t="n"/>
-      <c r="O46" s="116" t="n"/>
+      <c r="G46" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="P46" s="116" t="n">
-        <v>16322.7</v>
+        <v>32364</v>
       </c>
     </row>
     <row r="47" ht="35.25" customHeight="1" s="134">
@@ -14358,21 +14558,41 @@
         </is>
       </c>
       <c r="D47" s="119" t="n">
-        <v>2897.7</v>
-      </c>
-      <c r="E47" s="119" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="E47" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F47" s="119" t="n"/>
-      <c r="G47" s="119" t="n"/>
-      <c r="H47" s="119" t="n"/>
-      <c r="I47" s="119" t="n"/>
-      <c r="J47" s="119" t="n"/>
-      <c r="K47" s="119" t="n"/>
-      <c r="L47" s="119" t="n"/>
-      <c r="M47" s="119" t="n"/>
-      <c r="N47" s="119" t="n"/>
-      <c r="O47" s="119" t="n"/>
+      <c r="G47" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P47" s="119" t="n">
-        <v>2897.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" ht="35.25" customHeight="1" s="134">
@@ -14394,19 +14614,39 @@
       <c r="D48" s="119" t="n">
         <v>13425</v>
       </c>
-      <c r="E48" s="119" t="n"/>
+      <c r="E48" s="119" t="n">
+        <v>18939</v>
+      </c>
       <c r="F48" s="119" t="n"/>
-      <c r="G48" s="119" t="n"/>
-      <c r="H48" s="119" t="n"/>
-      <c r="I48" s="119" t="n"/>
-      <c r="J48" s="119" t="n"/>
-      <c r="K48" s="119" t="n"/>
-      <c r="L48" s="119" t="n"/>
-      <c r="M48" s="119" t="n"/>
-      <c r="N48" s="119" t="n"/>
-      <c r="O48" s="119" t="n"/>
+      <c r="G48" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P48" s="119" t="n">
-        <v>13425</v>
+        <v>32364</v>
       </c>
     </row>
     <row r="49" ht="35.25" customHeight="1" s="134">
@@ -14425,9 +14665,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D49" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D49" s="116" t="n"/>
       <c r="E49" s="116" t="n"/>
       <c r="F49" s="116" t="n"/>
       <c r="G49" s="116" t="n"/>
@@ -14459,9 +14697,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D50" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D50" s="119" t="n"/>
       <c r="E50" s="119" t="n"/>
       <c r="F50" s="119" t="n"/>
       <c r="G50" s="119" t="n"/>
@@ -14493,9 +14729,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D51" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D51" s="119" t="n"/>
       <c r="E51" s="119" t="n"/>
       <c r="F51" s="119" t="n"/>
       <c r="G51" s="119" t="n"/>
@@ -14527,9 +14761,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D52" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D52" s="116" t="n"/>
       <c r="E52" s="116" t="n"/>
       <c r="F52" s="116" t="n"/>
       <c r="G52" s="116" t="n"/>
@@ -14561,9 +14793,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D53" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D53" s="119" t="n"/>
       <c r="E53" s="119" t="n"/>
       <c r="F53" s="119" t="n"/>
       <c r="G53" s="119" t="n"/>
@@ -14595,9 +14825,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D54" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D54" s="119" t="n"/>
       <c r="E54" s="119" t="n"/>
       <c r="F54" s="119" t="n"/>
       <c r="G54" s="119" t="n"/>
@@ -14629,9 +14857,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D55" s="116" t="n">
-        <v>1066</v>
-      </c>
+      <c r="D55" s="116" t="n"/>
       <c r="E55" s="116" t="n"/>
       <c r="F55" s="116" t="n"/>
       <c r="G55" s="116" t="n"/>
@@ -14644,7 +14870,7 @@
       <c r="N55" s="116" t="n"/>
       <c r="O55" s="116" t="n"/>
       <c r="P55" s="116" t="n">
-        <v>1066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" ht="35.25" customHeight="1" s="134">
@@ -14663,9 +14889,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D56" s="119" t="n">
-        <v>1066</v>
-      </c>
+      <c r="D56" s="119" t="n"/>
       <c r="E56" s="119" t="n"/>
       <c r="F56" s="119" t="n"/>
       <c r="G56" s="119" t="n"/>
@@ -14678,7 +14902,7 @@
       <c r="N56" s="119" t="n"/>
       <c r="O56" s="119" t="n"/>
       <c r="P56" s="119" t="n">
-        <v>1066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" ht="35.25" customHeight="1" s="134">
@@ -14697,9 +14921,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D57" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D57" s="119" t="n"/>
       <c r="E57" s="119" t="n"/>
       <c r="F57" s="119" t="n"/>
       <c r="G57" s="119" t="n"/>
@@ -14731,9 +14953,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D58" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D58" s="116" t="n"/>
       <c r="E58" s="116" t="n"/>
       <c r="F58" s="116" t="n"/>
       <c r="G58" s="116" t="n"/>
@@ -14765,9 +14985,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D59" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D59" s="119" t="n"/>
       <c r="E59" s="119" t="n"/>
       <c r="F59" s="119" t="n"/>
       <c r="G59" s="119" t="n"/>
@@ -14799,9 +15017,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D60" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D60" s="119" t="n"/>
       <c r="E60" s="119" t="n"/>
       <c r="F60" s="119" t="n"/>
       <c r="G60" s="119" t="n"/>
@@ -14836,19 +15052,39 @@
       <c r="D61" s="116" t="n">
         <v>7912.81</v>
       </c>
-      <c r="E61" s="116" t="n"/>
+      <c r="E61" s="116" t="n">
+        <v>20737.16</v>
+      </c>
       <c r="F61" s="116" t="n"/>
-      <c r="G61" s="116" t="n"/>
-      <c r="H61" s="116" t="n"/>
-      <c r="I61" s="116" t="n"/>
-      <c r="J61" s="116" t="n"/>
-      <c r="K61" s="116" t="n"/>
-      <c r="L61" s="116" t="n"/>
-      <c r="M61" s="116" t="n"/>
-      <c r="N61" s="116" t="n"/>
-      <c r="O61" s="116" t="n"/>
+      <c r="G61" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="P61" s="116" t="n">
-        <v>7912.81</v>
+        <v>28649.97</v>
       </c>
     </row>
     <row r="62" ht="35.25" customHeight="1" s="134">
@@ -14870,17 +15106,37 @@
       <c r="D62" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="119" t="n"/>
+      <c r="E62" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F62" s="119" t="n"/>
-      <c r="G62" s="119" t="n"/>
-      <c r="H62" s="119" t="n"/>
-      <c r="I62" s="119" t="n"/>
-      <c r="J62" s="119" t="n"/>
-      <c r="K62" s="119" t="n"/>
-      <c r="L62" s="119" t="n"/>
-      <c r="M62" s="119" t="n"/>
-      <c r="N62" s="119" t="n"/>
-      <c r="O62" s="119" t="n"/>
+      <c r="G62" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P62" s="119" t="n">
         <v>0</v>
       </c>
@@ -14904,19 +15160,39 @@
       <c r="D63" s="119" t="n">
         <v>7912.81</v>
       </c>
-      <c r="E63" s="119" t="n"/>
+      <c r="E63" s="119" t="n">
+        <v>20737.16</v>
+      </c>
       <c r="F63" s="119" t="n"/>
-      <c r="G63" s="119" t="n"/>
-      <c r="H63" s="119" t="n"/>
-      <c r="I63" s="119" t="n"/>
-      <c r="J63" s="119" t="n"/>
-      <c r="K63" s="119" t="n"/>
-      <c r="L63" s="119" t="n"/>
-      <c r="M63" s="119" t="n"/>
-      <c r="N63" s="119" t="n"/>
-      <c r="O63" s="119" t="n"/>
+      <c r="G63" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P63" s="119" t="n">
-        <v>7912.81</v>
+        <v>28649.97</v>
       </c>
     </row>
     <row r="64" ht="35.25" customHeight="1" s="134">
@@ -14935,9 +15211,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D64" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D64" s="116" t="n"/>
       <c r="E64" s="116" t="n"/>
       <c r="F64" s="116" t="n"/>
       <c r="G64" s="116" t="n"/>
@@ -14969,9 +15243,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D65" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D65" s="119" t="n"/>
       <c r="E65" s="119" t="n"/>
       <c r="F65" s="119" t="n"/>
       <c r="G65" s="119" t="n"/>
@@ -15003,9 +15275,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D66" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D66" s="119" t="n"/>
       <c r="E66" s="119" t="n"/>
       <c r="F66" s="119" t="n"/>
       <c r="G66" s="119" t="n"/>
@@ -15040,19 +15310,39 @@
       <c r="D67" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="116" t="n"/>
+      <c r="E67" s="116" t="n">
+        <v>3030.71</v>
+      </c>
       <c r="F67" s="116" t="n"/>
-      <c r="G67" s="116" t="n"/>
-      <c r="H67" s="116" t="n"/>
-      <c r="I67" s="116" t="n"/>
-      <c r="J67" s="116" t="n"/>
-      <c r="K67" s="116" t="n"/>
-      <c r="L67" s="116" t="n"/>
-      <c r="M67" s="116" t="n"/>
-      <c r="N67" s="116" t="n"/>
-      <c r="O67" s="116" t="n"/>
+      <c r="G67" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="P67" s="116" t="n">
-        <v>0</v>
+        <v>3030.71</v>
       </c>
     </row>
     <row r="68" ht="35.25" customHeight="1" s="134">
@@ -15074,17 +15364,37 @@
       <c r="D68" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E68" s="119" t="n"/>
+      <c r="E68" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F68" s="119" t="n"/>
-      <c r="G68" s="119" t="n"/>
-      <c r="H68" s="119" t="n"/>
-      <c r="I68" s="119" t="n"/>
-      <c r="J68" s="119" t="n"/>
-      <c r="K68" s="119" t="n"/>
-      <c r="L68" s="119" t="n"/>
-      <c r="M68" s="119" t="n"/>
-      <c r="N68" s="119" t="n"/>
-      <c r="O68" s="119" t="n"/>
+      <c r="G68" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P68" s="119" t="n">
         <v>0</v>
       </c>
@@ -15108,19 +15418,39 @@
       <c r="D69" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="119" t="n"/>
+      <c r="E69" s="119" t="n">
+        <v>3030.71</v>
+      </c>
       <c r="F69" s="119" t="n"/>
-      <c r="G69" s="119" t="n"/>
-      <c r="H69" s="119" t="n"/>
-      <c r="I69" s="119" t="n"/>
-      <c r="J69" s="119" t="n"/>
-      <c r="K69" s="119" t="n"/>
-      <c r="L69" s="119" t="n"/>
-      <c r="M69" s="119" t="n"/>
-      <c r="N69" s="119" t="n"/>
-      <c r="O69" s="119" t="n"/>
+      <c r="G69" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P69" s="119" t="n">
-        <v>0</v>
+        <v>3030.71</v>
       </c>
     </row>
     <row r="70" ht="35.25" customHeight="1" s="134">
@@ -15139,9 +15469,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D70" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D70" s="116" t="n"/>
       <c r="E70" s="116" t="n"/>
       <c r="F70" s="116" t="n"/>
       <c r="G70" s="116" t="n"/>
@@ -15173,9 +15501,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D71" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D71" s="119" t="n"/>
       <c r="E71" s="119" t="n"/>
       <c r="F71" s="119" t="n"/>
       <c r="G71" s="119" t="n"/>
@@ -15207,9 +15533,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D72" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D72" s="119" t="n"/>
       <c r="E72" s="119" t="n"/>
       <c r="F72" s="119" t="n"/>
       <c r="G72" s="119" t="n"/>
@@ -15241,9 +15565,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D73" s="116" t="n">
-        <v>3041.3</v>
-      </c>
+      <c r="D73" s="116" t="n"/>
       <c r="E73" s="116" t="n"/>
       <c r="F73" s="116" t="n"/>
       <c r="G73" s="116" t="n"/>
@@ -15256,7 +15578,7 @@
       <c r="N73" s="116" t="n"/>
       <c r="O73" s="116" t="n"/>
       <c r="P73" s="116" t="n">
-        <v>3041.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" ht="35.25" customHeight="1" s="134">
@@ -15275,9 +15597,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D74" s="119" t="n">
-        <v>3041.3</v>
-      </c>
+      <c r="D74" s="119" t="n"/>
       <c r="E74" s="119" t="n"/>
       <c r="F74" s="119" t="n"/>
       <c r="G74" s="119" t="n"/>
@@ -15290,7 +15610,7 @@
       <c r="N74" s="119" t="n"/>
       <c r="O74" s="119" t="n"/>
       <c r="P74" s="119" t="n">
-        <v>3041.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" ht="35.25" customHeight="1" s="134">
@@ -15309,9 +15629,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D75" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D75" s="119" t="n"/>
       <c r="E75" s="119" t="n"/>
       <c r="F75" s="119" t="n"/>
       <c r="G75" s="119" t="n"/>
@@ -15343,9 +15661,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D76" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D76" s="116" t="n"/>
       <c r="E76" s="116" t="n"/>
       <c r="F76" s="116" t="n"/>
       <c r="G76" s="116" t="n"/>
@@ -15377,9 +15693,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D77" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D77" s="119" t="n"/>
       <c r="E77" s="119" t="n"/>
       <c r="F77" s="119" t="n"/>
       <c r="G77" s="119" t="n"/>
@@ -15411,9 +15725,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D78" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D78" s="119" t="n"/>
       <c r="E78" s="119" t="n"/>
       <c r="F78" s="119" t="n"/>
       <c r="G78" s="119" t="n"/>
@@ -15445,9 +15757,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D79" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D79" s="116" t="n"/>
       <c r="E79" s="116" t="n"/>
       <c r="F79" s="116" t="n"/>
       <c r="G79" s="116" t="n"/>
@@ -15479,9 +15789,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D80" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D80" s="119" t="n"/>
       <c r="E80" s="119" t="n"/>
       <c r="F80" s="119" t="n"/>
       <c r="G80" s="119" t="n"/>
@@ -15513,9 +15821,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D81" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D81" s="119" t="n"/>
       <c r="E81" s="119" t="n"/>
       <c r="F81" s="119" t="n"/>
       <c r="G81" s="119" t="n"/>
@@ -15550,19 +15856,39 @@
       <c r="D82" s="116" t="n">
         <v>2546</v>
       </c>
-      <c r="E82" s="116" t="n"/>
+      <c r="E82" s="116" t="n">
+        <v>8195</v>
+      </c>
       <c r="F82" s="116" t="n"/>
-      <c r="G82" s="116" t="n"/>
-      <c r="H82" s="116" t="n"/>
-      <c r="I82" s="116" t="n"/>
-      <c r="J82" s="116" t="n"/>
-      <c r="K82" s="116" t="n"/>
-      <c r="L82" s="116" t="n"/>
-      <c r="M82" s="116" t="n"/>
-      <c r="N82" s="116" t="n"/>
-      <c r="O82" s="116" t="n"/>
+      <c r="G82" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="P82" s="116" t="n">
-        <v>2546</v>
+        <v>10741</v>
       </c>
     </row>
     <row r="83" ht="35.25" customHeight="1" s="134">
@@ -15584,17 +15910,37 @@
       <c r="D83" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E83" s="119" t="n"/>
+      <c r="E83" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F83" s="119" t="n"/>
-      <c r="G83" s="119" t="n"/>
-      <c r="H83" s="119" t="n"/>
-      <c r="I83" s="119" t="n"/>
-      <c r="J83" s="119" t="n"/>
-      <c r="K83" s="119" t="n"/>
-      <c r="L83" s="119" t="n"/>
-      <c r="M83" s="119" t="n"/>
-      <c r="N83" s="119" t="n"/>
-      <c r="O83" s="119" t="n"/>
+      <c r="G83" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P83" s="119" t="n">
         <v>0</v>
       </c>
@@ -15618,19 +15964,39 @@
       <c r="D84" s="119" t="n">
         <v>2546</v>
       </c>
-      <c r="E84" s="119" t="n"/>
+      <c r="E84" s="119" t="n">
+        <v>8195</v>
+      </c>
       <c r="F84" s="119" t="n"/>
-      <c r="G84" s="119" t="n"/>
-      <c r="H84" s="119" t="n"/>
-      <c r="I84" s="119" t="n"/>
-      <c r="J84" s="119" t="n"/>
-      <c r="K84" s="119" t="n"/>
-      <c r="L84" s="119" t="n"/>
-      <c r="M84" s="119" t="n"/>
-      <c r="N84" s="119" t="n"/>
-      <c r="O84" s="119" t="n"/>
+      <c r="G84" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P84" s="119" t="n">
-        <v>2546</v>
+        <v>10741</v>
       </c>
     </row>
     <row r="85" ht="35.25" customHeight="1" s="134">
@@ -15652,17 +16018,37 @@
       <c r="D85" s="116" t="n">
         <v>6924</v>
       </c>
-      <c r="E85" s="116" t="n"/>
+      <c r="E85" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="F85" s="116" t="n"/>
-      <c r="G85" s="116" t="n"/>
-      <c r="H85" s="116" t="n"/>
-      <c r="I85" s="116" t="n"/>
-      <c r="J85" s="116" t="n"/>
-      <c r="K85" s="116" t="n"/>
-      <c r="L85" s="116" t="n"/>
-      <c r="M85" s="116" t="n"/>
-      <c r="N85" s="116" t="n"/>
-      <c r="O85" s="116" t="n"/>
+      <c r="G85" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="P85" s="116" t="n">
         <v>6924</v>
       </c>
@@ -15686,17 +16072,37 @@
       <c r="D86" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E86" s="119" t="n"/>
+      <c r="E86" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F86" s="119" t="n"/>
-      <c r="G86" s="119" t="n"/>
-      <c r="H86" s="119" t="n"/>
-      <c r="I86" s="119" t="n"/>
-      <c r="J86" s="119" t="n"/>
-      <c r="K86" s="119" t="n"/>
-      <c r="L86" s="119" t="n"/>
-      <c r="M86" s="119" t="n"/>
-      <c r="N86" s="119" t="n"/>
-      <c r="O86" s="119" t="n"/>
+      <c r="G86" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P86" s="119" t="n">
         <v>0</v>
       </c>
@@ -15720,17 +16126,37 @@
       <c r="D87" s="119" t="n">
         <v>6924</v>
       </c>
-      <c r="E87" s="119" t="n"/>
+      <c r="E87" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F87" s="119" t="n"/>
-      <c r="G87" s="119" t="n"/>
-      <c r="H87" s="119" t="n"/>
-      <c r="I87" s="119" t="n"/>
-      <c r="J87" s="119" t="n"/>
-      <c r="K87" s="119" t="n"/>
-      <c r="L87" s="119" t="n"/>
-      <c r="M87" s="119" t="n"/>
-      <c r="N87" s="119" t="n"/>
-      <c r="O87" s="119" t="n"/>
+      <c r="G87" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P87" s="119" t="n">
         <v>6924</v>
       </c>
@@ -15754,17 +16180,37 @@
       <c r="D88" s="116" t="n">
         <v>4269.55</v>
       </c>
-      <c r="E88" s="116" t="n"/>
+      <c r="E88" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="F88" s="116" t="n"/>
-      <c r="G88" s="116" t="n"/>
-      <c r="H88" s="116" t="n"/>
-      <c r="I88" s="116" t="n"/>
-      <c r="J88" s="116" t="n"/>
-      <c r="K88" s="116" t="n"/>
-      <c r="L88" s="116" t="n"/>
-      <c r="M88" s="116" t="n"/>
-      <c r="N88" s="116" t="n"/>
-      <c r="O88" s="116" t="n"/>
+      <c r="G88" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="P88" s="116" t="n">
         <v>4269.55</v>
       </c>
@@ -15788,17 +16234,37 @@
       <c r="D89" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E89" s="119" t="n"/>
+      <c r="E89" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F89" s="119" t="n"/>
-      <c r="G89" s="119" t="n"/>
-      <c r="H89" s="119" t="n"/>
-      <c r="I89" s="119" t="n"/>
-      <c r="J89" s="119" t="n"/>
-      <c r="K89" s="119" t="n"/>
-      <c r="L89" s="119" t="n"/>
-      <c r="M89" s="119" t="n"/>
-      <c r="N89" s="119" t="n"/>
-      <c r="O89" s="119" t="n"/>
+      <c r="G89" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P89" s="119" t="n">
         <v>0</v>
       </c>
@@ -15822,17 +16288,37 @@
       <c r="D90" s="119" t="n">
         <v>4269.55</v>
       </c>
-      <c r="E90" s="119" t="n"/>
+      <c r="E90" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F90" s="119" t="n"/>
-      <c r="G90" s="119" t="n"/>
-      <c r="H90" s="119" t="n"/>
-      <c r="I90" s="119" t="n"/>
-      <c r="J90" s="119" t="n"/>
-      <c r="K90" s="119" t="n"/>
-      <c r="L90" s="119" t="n"/>
-      <c r="M90" s="119" t="n"/>
-      <c r="N90" s="119" t="n"/>
-      <c r="O90" s="119" t="n"/>
+      <c r="G90" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P90" s="119" t="n">
         <v>4269.55</v>
       </c>
@@ -15853,9 +16339,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D91" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D91" s="116" t="n"/>
       <c r="E91" s="116" t="n"/>
       <c r="F91" s="116" t="n"/>
       <c r="G91" s="116" t="n"/>
@@ -15887,9 +16371,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D92" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D92" s="119" t="n"/>
       <c r="E92" s="119" t="n"/>
       <c r="F92" s="119" t="n"/>
       <c r="G92" s="119" t="n"/>
@@ -15921,9 +16403,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D93" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D93" s="119" t="n"/>
       <c r="E93" s="119" t="n"/>
       <c r="F93" s="119" t="n"/>
       <c r="G93" s="119" t="n"/>
@@ -15958,17 +16438,37 @@
       <c r="D94" s="116" t="n">
         <v>10317.24</v>
       </c>
-      <c r="E94" s="116" t="n"/>
+      <c r="E94" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="F94" s="116" t="n"/>
-      <c r="G94" s="116" t="n"/>
-      <c r="H94" s="116" t="n"/>
-      <c r="I94" s="116" t="n"/>
-      <c r="J94" s="116" t="n"/>
-      <c r="K94" s="116" t="n"/>
-      <c r="L94" s="116" t="n"/>
-      <c r="M94" s="116" t="n"/>
-      <c r="N94" s="116" t="n"/>
-      <c r="O94" s="116" t="n"/>
+      <c r="G94" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="116" t="n">
+        <v>0</v>
+      </c>
       <c r="P94" s="116" t="n">
         <v>10317.24</v>
       </c>
@@ -15992,17 +16492,37 @@
       <c r="D95" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="119" t="n"/>
+      <c r="E95" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F95" s="119" t="n"/>
-      <c r="G95" s="119" t="n"/>
-      <c r="H95" s="119" t="n"/>
-      <c r="I95" s="119" t="n"/>
-      <c r="J95" s="119" t="n"/>
-      <c r="K95" s="119" t="n"/>
-      <c r="L95" s="119" t="n"/>
-      <c r="M95" s="119" t="n"/>
-      <c r="N95" s="119" t="n"/>
-      <c r="O95" s="119" t="n"/>
+      <c r="G95" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P95" s="119" t="n">
         <v>0</v>
       </c>
@@ -16026,17 +16546,37 @@
       <c r="D96" s="119" t="n">
         <v>10317.24</v>
       </c>
-      <c r="E96" s="119" t="n"/>
+      <c r="E96" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="F96" s="119" t="n"/>
-      <c r="G96" s="119" t="n"/>
-      <c r="H96" s="119" t="n"/>
-      <c r="I96" s="119" t="n"/>
-      <c r="J96" s="119" t="n"/>
-      <c r="K96" s="119" t="n"/>
-      <c r="L96" s="119" t="n"/>
-      <c r="M96" s="119" t="n"/>
-      <c r="N96" s="119" t="n"/>
-      <c r="O96" s="119" t="n"/>
+      <c r="G96" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="119" t="n">
+        <v>0</v>
+      </c>
       <c r="P96" s="119" t="n">
         <v>10317.24</v>
       </c>
@@ -16057,9 +16597,7 @@
           <t>Total requalificado (m2)</t>
         </is>
       </c>
-      <c r="D97" s="116" t="n">
-        <v>0</v>
-      </c>
+      <c r="D97" s="116" t="n"/>
       <c r="E97" s="116" t="n"/>
       <c r="F97" s="116" t="n"/>
       <c r="G97" s="116" t="n"/>
@@ -16091,9 +16629,7 @@
           <t>SMSUB/CONVIAS</t>
         </is>
       </c>
-      <c r="D98" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D98" s="119" t="n"/>
       <c r="E98" s="119" t="n"/>
       <c r="F98" s="119" t="n"/>
       <c r="G98" s="119" t="n"/>
@@ -16125,9 +16661,7 @@
           <t>SMSUB/CONSEMAVI</t>
         </is>
       </c>
-      <c r="D99" s="119" t="n">
-        <v>0</v>
-      </c>
+      <c r="D99" s="119" t="n"/>
       <c r="E99" s="119" t="n"/>
       <c r="F99" s="119" t="n"/>
       <c r="G99" s="119" t="n"/>
@@ -16152,10 +16686,10 @@
       <c r="B100" s="138" t="n"/>
       <c r="C100" s="136" t="n"/>
       <c r="D100" s="121" t="n">
-        <v>72870.70000000001</v>
+        <v>63025.6</v>
       </c>
       <c r="E100" s="121" t="n">
-        <v>0</v>
+        <v>87326.38</v>
       </c>
       <c r="F100" s="121" t="n">
         <v>0</v>
@@ -16188,7 +16722,7 @@
         <v>0</v>
       </c>
       <c r="P100" s="121" t="n">
-        <v>72870.70000000001</v>
+        <v>150351.98</v>
       </c>
     </row>
     <row r="101" ht="35.25" customHeight="1" s="134">
